--- a/backend/apps/contracts/document_templates/cmr_en.xlsx
+++ b/backend/apps/contracts/document_templates/cmr_en.xlsx
@@ -9,7 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CMR EN" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'CMR EN'!$A$1:$N$53</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'CMR EN'!$A$1:$N$54</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
